--- a/Compititor's_Price/Ecotherm_Prices/Ecotherm_Prices_09-02-2026.xlsx
+++ b/Compititor's_Price/Ecotherm_Prices/Ecotherm_Prices_09-02-2026.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="160">
   <si>
     <t>SKU</t>
   </si>
@@ -430,49 +430,25 @@
     <t>£76.10</t>
   </si>
   <si>
-    <t>£20.12</t>
-  </si>
-  <si>
-    <t>£23.53</t>
-  </si>
-  <si>
-    <t>£27.12</t>
-  </si>
-  <si>
-    <t>£27.66</t>
-  </si>
-  <si>
-    <t>£34.27</t>
-  </si>
-  <si>
-    <t>£38.38</t>
-  </si>
-  <si>
-    <t>£38.49</t>
-  </si>
-  <si>
-    <t>£43.34</t>
-  </si>
-  <si>
-    <t>£47.25</t>
-  </si>
-  <si>
-    <t>£43.99</t>
-  </si>
-  <si>
-    <t>£60.72</t>
-  </si>
-  <si>
-    <t>£57.19</t>
-  </si>
-  <si>
-    <t>£65.34</t>
-  </si>
-  <si>
-    <t>£68.75</t>
-  </si>
-  <si>
-    <t>£67.65</t>
+    <t>£12.15</t>
+  </si>
+  <si>
+    <t>£19.75</t>
+  </si>
+  <si>
+    <t>£25.47</t>
+  </si>
+  <si>
+    <t>£33.99</t>
+  </si>
+  <si>
+    <t>£33.38</t>
+  </si>
+  <si>
+    <t>£40.99</t>
+  </si>
+  <si>
+    <t>£42.35</t>
   </si>
   <si>
     <t>Add to Enquiry</t>
@@ -957,13 +933,13 @@
         <v>123</v>
       </c>
       <c r="L2" t="s">
-        <v>138</v>
+        <v>44</v>
       </c>
       <c r="M2" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="N2" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
     </row>
     <row r="3" spans="1:14">
@@ -1001,13 +977,13 @@
         <v>124</v>
       </c>
       <c r="L3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="M3" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="N3" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -1045,13 +1021,13 @@
         <v>125</v>
       </c>
       <c r="L4" t="s">
-        <v>140</v>
+        <v>46</v>
       </c>
       <c r="M4" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="N4" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -1089,13 +1065,13 @@
         <v>126</v>
       </c>
       <c r="L5" t="s">
-        <v>141</v>
+        <v>47</v>
       </c>
       <c r="M5" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="N5" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -1133,13 +1109,13 @@
         <v>127</v>
       </c>
       <c r="L6" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="M6" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="N6" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -1177,10 +1153,10 @@
         <v>128</v>
       </c>
       <c r="L7" t="s">
-        <v>143</v>
+        <v>62</v>
       </c>
       <c r="M7" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="N7" t="s">
         <v>68</v>
@@ -1221,13 +1197,13 @@
         <v>129</v>
       </c>
       <c r="L8" t="s">
-        <v>144</v>
+        <v>50</v>
       </c>
       <c r="M8" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="N8" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -1265,13 +1241,13 @@
         <v>130</v>
       </c>
       <c r="L9" t="s">
+        <v>140</v>
+      </c>
+      <c r="M9" t="s">
         <v>145</v>
       </c>
-      <c r="M9" t="s">
-        <v>153</v>
-      </c>
       <c r="N9" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -1309,13 +1285,13 @@
         <v>131</v>
       </c>
       <c r="L10" t="s">
-        <v>146</v>
+        <v>52</v>
       </c>
       <c r="M10" t="s">
+        <v>145</v>
+      </c>
+      <c r="N10" t="s">
         <v>153</v>
-      </c>
-      <c r="N10" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -1353,13 +1329,13 @@
         <v>132</v>
       </c>
       <c r="L11" t="s">
-        <v>147</v>
+        <v>53</v>
       </c>
       <c r="M11" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="N11" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -1397,13 +1373,13 @@
         <v>133</v>
       </c>
       <c r="L12" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="M12" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="N12" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -1441,13 +1417,13 @@
         <v>134</v>
       </c>
       <c r="L13" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="M13" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="N13" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
     </row>
     <row r="14" spans="1:14">
@@ -1485,13 +1461,13 @@
         <v>135</v>
       </c>
       <c r="L14" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="M14" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="N14" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -1529,13 +1505,13 @@
         <v>136</v>
       </c>
       <c r="L15" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="M15" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="N15" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -1573,13 +1549,13 @@
         <v>137</v>
       </c>
       <c r="L16" t="s">
-        <v>152</v>
+        <v>58</v>
       </c>
       <c r="M16" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="N16" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
     </row>
   </sheetData>
